--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1218-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1218-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F05D26B8-6332-4045-8B5C-3C6912876A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{198FEFBA-B9DC-4A9C-AA2B-8CBE5E2F3B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{2B755BA5-3248-40E3-8288-78299248667A}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{6660F594-7527-47EE-9F58-26729BCC2BA7}"/>
   </bookViews>
   <sheets>
     <sheet name="1218-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1478,21 +1478,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E455DE-6E1A-4616-A135-125579717134}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125966A3-690C-4838-947E-12934A98692A}">
   <dimension ref="A1:R62"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="7" width="8" customWidth="1"/>
-    <col min="8" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="7" width="10" customWidth="1"/>
+    <col min="8" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1520,7 +1520,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1550,7 +1550,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1646,7 +1646,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="40">
         <v>2024</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="38">
         <v>2023</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="40">
         <v>2022</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>25</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="38">
         <v>2021</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <v>2020</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="38">
         <v>2019</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="40">
         <v>2018</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="38">
         <v>2017</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
         <v>2016</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="38">
         <v>2015</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="40">
         <v>2014</v>
       </c>
@@ -3246,7 +3246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="38">
         <v>2013</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="40">
         <v>2012</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="38">
         <v>2011</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="40">
         <v>2010</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="38">
         <v>2009</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="40">
         <v>2008</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="38">
         <v>2007</v>
       </c>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="40">
         <v>2006</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="38">
         <v>2005</v>
       </c>
@@ -3732,7 +3732,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="40">
         <v>2004</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="38">
         <v>2003</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="40">
         <v>2002</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="38">
         <v>2001</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="40">
         <v>2000</v>
       </c>
@@ -4002,7 +4002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="38">
         <v>1999</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="40">
         <v>1998</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="38">
         <v>1997</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="40">
         <v>1996</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="38">
         <v>1995</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="40">
         <v>1994</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>3.11</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="38">
         <v>1993</v>
       </c>
@@ -4380,7 +4380,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="40">
         <v>1992</v>
       </c>
@@ -4434,7 +4434,7 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="38">
         <v>1991</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="40">
         <v>1990</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="38">
         <v>1989</v>
       </c>
@@ -4596,7 +4596,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="40">
         <v>1988</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="38">
         <v>1987</v>
       </c>
@@ -4704,7 +4704,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="40">
         <v>1986</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="38" t="s">
         <v>44</v>
       </c>
